--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.76103016551392</v>
+        <v>2.236167401896012</v>
       </c>
       <c r="D2" t="n">
-        <v>11.98080395722834</v>
+        <v>1.946880643049606</v>
       </c>
       <c r="E2" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F2" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.57357338061747</v>
+        <v>1.718205674350338</v>
       </c>
       <c r="D3" t="n">
-        <v>10.22935383580474</v>
+        <v>1.66226999831827</v>
       </c>
       <c r="E3" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F3" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.14848712221734</v>
+        <v>4.411629157360318</v>
       </c>
       <c r="D4" t="n">
-        <v>27.2948396156065</v>
+        <v>4.435411437536056</v>
       </c>
       <c r="E4" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F4" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.9287152800165</v>
+        <v>1.775916233002681</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24098047441528</v>
+        <v>1.989159327092483</v>
       </c>
       <c r="E5" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F5" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.68305861426396</v>
+        <v>2.223497024817894</v>
       </c>
       <c r="D6" t="n">
-        <v>13.12840199784524</v>
+        <v>2.133365324649851</v>
       </c>
       <c r="E6" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F6" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.89507110568792</v>
+        <v>3.070449054674286</v>
       </c>
       <c r="D7" t="n">
-        <v>19.89265131599266</v>
+        <v>3.232555838848806</v>
       </c>
       <c r="E7" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F7" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.43501262666338</v>
+        <v>3.3206895518328</v>
       </c>
       <c r="D8" t="n">
-        <v>19.3808207084693</v>
+        <v>3.149383365126261</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F8" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.19012850697569</v>
+        <v>1.818395882383549</v>
       </c>
       <c r="D9" t="n">
-        <v>18.0840539102541</v>
+        <v>2.938658760416291</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F9" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.267858436716327</v>
+        <v>1.018526995966403</v>
       </c>
       <c r="D10" t="n">
-        <v>6.500534166085465</v>
+        <v>1.056336801988888</v>
       </c>
       <c r="E10" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F10" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.08974887619781</v>
+        <v>3.914584192382145</v>
       </c>
       <c r="D11" t="n">
-        <v>2.070478639824348</v>
+        <v>0.3364527789714565</v>
       </c>
       <c r="E11" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F11" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.01115993009697</v>
+        <v>4.551813488640757</v>
       </c>
       <c r="D12" t="n">
-        <v>36.55332515149654</v>
+        <v>5.939915337118188</v>
       </c>
       <c r="E12" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F12" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>64.30500515384182</v>
+        <v>10.4495633374993</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1245154965971</v>
+        <v>2.620233768197028</v>
       </c>
       <c r="E13" t="n">
-        <v>14.73464941989665</v>
+        <v>2.394380530733205</v>
       </c>
       <c r="F13" t="n">
-        <v>8.835880153827182</v>
+        <v>1.435830524996917</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
